--- a/DemandaEnergetica/Carbon_termico/Carbón Termico.xlsx
+++ b/DemandaEnergetica/Carbon_termico/Carbón Termico.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="312">
   <si>
     <t xml:space="preserve">Trimestre de Fecha Resolucion</t>
   </si>
@@ -967,7 +967,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -993,6 +993,13 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -1039,7 +1046,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1066,6 +1073,10 @@
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1436,10 +1447,18 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="A4" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E4" s="5" t="s">
         <v>82</v>
       </c>
@@ -1448,10 +1467,18 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="A5" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E5" s="5" t="s">
         <v>83</v>
       </c>
@@ -1460,10 +1487,18 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="A6" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E6" s="5" t="s">
         <v>84</v>
       </c>
@@ -1472,22 +1507,39 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="A7" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E7" s="5" t="s">
         <v>85</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10000</v>
       </c>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="A8" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E8" s="5" t="s">
         <v>86</v>
       </c>
@@ -1496,10 +1548,18 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="A9" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E9" s="5" t="s">
         <v>87</v>
       </c>
@@ -1508,10 +1568,18 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="A10" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E10" s="5" t="s">
         <v>88</v>
       </c>
@@ -1520,10 +1588,18 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="A11" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E11" s="5" t="s">
         <v>89</v>
       </c>
@@ -1532,10 +1608,18 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="A12" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E12" s="5" t="s">
         <v>90</v>
       </c>
@@ -1544,10 +1628,18 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E13" s="5" t="s">
         <v>91</v>
       </c>
@@ -1556,10 +1648,18 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="A14" s="4" t="n">
+        <v>35064</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="E14" s="5" t="s">
         <v>92</v>
       </c>
@@ -13750,12 +13850,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="336">
+  <mergeCells count="332">
     <mergeCell ref="F1:CF1"/>
-    <mergeCell ref="A3:A14"/>
-    <mergeCell ref="B3:B14"/>
-    <mergeCell ref="C3:C14"/>
-    <mergeCell ref="D3:D14"/>
     <mergeCell ref="A15:A26"/>
     <mergeCell ref="B15:B26"/>
     <mergeCell ref="C15:C26"/>
